--- a/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64927_completo.xlsx
+++ b/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64927_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb80b31feae8f43e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra4a360581df5484f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7456</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64927_completo.xlsx
+++ b/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64927_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra4a360581df5484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R93273a29fae3437e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8705</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8269</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8084</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8171</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8118</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8118</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8118</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8071</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8069</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8121</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8069</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7973</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7883</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7973</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8266</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7404</x:v>
+        <x:v>      1.7377</x:v>
       </x:c>
     </x:row>
     <x:row>
